--- a/outputs/59511.xlsx
+++ b/outputs/59511.xlsx
@@ -129,32 +129,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="15" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="15" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="15" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="15" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -410,201 +414,201 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="10.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E1" s="1"/>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="7" t="n">
         <f aca="false">ROUNDUP(E2/1000,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <f aca="false">A2+1001</f>
         <v>1001</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <f aca="false">B2+1000</f>
         <v>2000</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <f aca="false">ROUNDUP(E3/1000,0)</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <f aca="false">A3+1000</f>
         <v>2001</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <f aca="false">B3+1000</f>
         <v>3000</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <f aca="false">ROUNDUP(E4/1000,0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <f aca="false">A4+1000</f>
         <v>3001</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <f aca="false">B4+1000</f>
         <v>4000</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>7200</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <f aca="false">ROUNDUP(E5/1000,0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <f aca="false">A5+1000</f>
         <v>4001</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <f aca="false">B5+1000</f>
         <v>5000</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>8500</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <f aca="false">ROUNDUP(E6/1000,0)</f>
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <f aca="false">A6+1000</f>
         <v>5001</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <f aca="false">B6+1000</f>
         <v>6000</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <f aca="false">A7+1000</f>
         <v>6001</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <f aca="false">B7+1000</f>
         <v>7000</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <f aca="false">A8+1000</f>
         <v>7001</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="4" t="n">
         <f aca="false">B8+1000</f>
         <v>8000</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <f aca="false">A9+1000</f>
         <v>8001</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <f aca="false">B9+1000</f>
         <v>9000</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <f aca="false">A10+1000</f>
         <v>9001</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="4" t="n">
         <f aca="false">B10+1000</f>
         <v>10000</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <f aca="false">A11+1000</f>
         <v>10001</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <f aca="false">B11+1000</f>
         <v>11000</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="1"/>
+      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/59511.xlsx
+++ b/outputs/59511.xlsx
@@ -439,7 +439,7 @@
         <v>300</v>
       </c>
       <c r="F2" s="7" t="n">
-        <f aca="false">ROUNDUP(E2/1000,0)</f>
+        <f aca="false">C2</f>
         <v>1</v>
       </c>
     </row>
@@ -459,7 +459,7 @@
         <v>2000</v>
       </c>
       <c r="F3" s="7" t="n">
-        <f aca="false">ROUNDUP(E3/1000,0)</f>
+        <f aca="false">C3</f>
         <v>2</v>
       </c>
     </row>
@@ -479,7 +479,7 @@
         <v>3000</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">ROUNDUP(E4/1000,0)</f>
+        <f aca="false">C4</f>
         <v>3</v>
       </c>
     </row>
@@ -499,8 +499,8 @@
         <v>7200</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">ROUNDUP(E5/1000,0)</f>
-        <v>8</v>
+        <f aca="false">C5</f>
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -519,8 +519,8 @@
         <v>8500</v>
       </c>
       <c r="F6" s="7" t="n">
-        <f aca="false">ROUNDUP(E6/1000,0)</f>
-        <v>9</v>
+        <f aca="false">C6</f>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
